--- a/data/exports/王颖瑜伽/dist_order_2026-09-04.xlsx
+++ b/data/exports/王颖瑜伽/dist_order_2026-09-04.xlsx
@@ -4489,7 +4489,7 @@
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>人生靠自己</t>
+          <t>人心易冷</t>
         </is>
       </c>
       <c r="C69" s="0" t="inlineStr">
